--- a/Evaluation/Exam 3 Grade.xlsx
+++ b/Evaluation/Exam 3 Grade.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GIT\00 daily\DailyFolder\Evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145E02C6-886F-40A1-A0D1-92E3432F659C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24806EE8-86E1-47AA-AE1E-CDE594B37A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="495" windowWidth="41730" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19425" yWindow="210" windowWidth="31665" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grading" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
   <si>
     <t>Name</t>
   </si>
@@ -211,13 +211,155 @@
   </si>
   <si>
     <t>Grade 3 - 20</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+Excellent implementation.
+Question 2 - Multithreading with coordination
+The requirement was to create 5 threads/tasks, but the code only creates 3 tasks.
+Sleep time should be random between 1 and 20 seconds, but your code sleeps between 100 and 999 milliseconds.
+Question 3 - Sets &amp; Dictionary 
+Case-insensitive retrieval not handled
+getWords(char letter) does not convert the input letter to lowercase.
+If a user calls getWords('T'), it will return null.</t>
+  </si>
+  <si>
+    <t>Question 3 - Sets &amp; Dictionary 
+Code works but has follwing issues
+getWords() returns a String instead of a data structure.
+Retrieval is not case-insensitive because letter is not converted to lowercase.
+Lookup is not efficient because it loops through all words each time instead of using a Map&lt;Character, Set&lt;String&gt;&gt;.</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+Any resources created should be properly closed.
+Resources are not fully closed.
+Question 2 - Multithreading with coordination
+CountDownLatch is created but never used by the worker threads, so tasks do not wait for a common start trigger.
+awaitTermination() is called before shutdown(), so it does not correctly wait for all tasks to complete.
+Final message may print before tasks finish. Final message may print before tasks finish.
+Question 3 - Sets &amp; Dictionary 
+Retrieval is not case-insensitive because letter is not converted to lowercase.
+getWords() loops through all words each time, lookup could be optimized with a map.</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+The required prompt was not used. It prints &gt;&gt;&gt; instead of: Either enter a value or Type EXIT to end:
+It is more about usability and readability aspect as user may not know what program as expecting to do.
+Question 2 - Multithreading with coordination
+Your code does not use a start trigger such as CountDownLatch, so threads start as they are started rather 
+than waiting until all are ready.
+Question 3 - Sets &amp; Dictionary 
+Excellent implementation</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+EXIT check is case-sensitive; requirement was case-insensitive. Server check for case insensitve "EXIT", will cause error
+Scanner is not closed.
+Question 2 - Multithreading with coordination
+The CountDownLatch is not used perfectly as a start trigger. Because countDown() happens inside the same loop that submits tasks, some tasks may begin after enough countdowns occur,
+rather than all being fully submitted first. However, the core coordination/concurrency idea is mostly correct.
+Question 3 - Sets &amp; Dictionary 
+getWords() is not case-insensitive because letter is not converted to lowercase.
+Lookup scans the full set each time rather than using a map organized by starting letter.</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+Excellent Implementation
+Question 2 - Multithreading with coordination
+Sleep duration is less than required; it uses 0–999 milliseconds instead of 1–20 seconds. Also, finish.countDown() happens before printing the completed message, 
+so the final message could theoretically print before the last completed message.
+Question 3 - Sets &amp; Dictionary
+Returns an array instead of a set/list-style collection, does not handle uppercase input letters, 
+and scans all words each time rather than using a map for efficient retrieval.
+Problem has compilation issue at return words.toArray(String[]);
+correct syntax is return words.toArray(new String[words.size()]);</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+Empty catch block hides errors.
+Use  System.out.println(in.nextLine ()) insted of System.out.println(in.next());
+in.next() prints tokens instead of full response lines
+Question 2 - Multithreading with coordination
+Excellent solution
+Question 3 - Sets &amp; Dictionary 
+Retrieval is not case-insensitive because first is not converted to lowercase.
+Lookup scans all words each time instead of using a map by starting letter would be a better solution</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+Does not send EXIT to the server, so the server may never know to stop and respond. After entering Exit, 
+You code hangs. You must send the Exit command before reading the resonse.
+You are using scanner.next() instead of nextLine(), so multi-word input would not work.
+Question 2 - Multithreading with coordination
+There are several issues with the code
+1. The started message is inside for(int i = 0; i &lt; i; i++), which never runs. You are calling thread::run, which has 
+   no impact with Executor service
+2. Does not print completed messages and Does not wait for all tasks to finish.
+3. Final message "All tasks completed." is missing.
+4. Program does not print required output.</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+1. Prompts for messages should be a continuous input loop.
+2. Check for Exit should be case insensitive. 
+3. Exit command is not send to Server. For server response, you need to 
+read atleast 2 incoming message.
+Question 2 - Multithreading with coordination
+Good Implementation.
+Question 3 - Sets &amp; Dictionary 
+There are several issues with the Implementation
+1. Cannot use enhanced for-loop directly on a String: for (String w : phrase).
+2. Cannot use enhanced for-loop on a char: for(char chr : letter).
+3. char does not have .equals().
+4. getWords() declares return type String but returns nothing.
+5. Does not retrieve words by starting letter.
+6. Program does not compile</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+1. Reads only one response line instead of both server response lines.
+2. Code creates a new Scanner and PrintWriter inside the loop each time. Not an effcient programming
+3. resources are not consistently closed.
+Question 2 - Multithreading with coordination
+Couple of issues with the Code1. 
+1 exec.shutdown() is called after awaitTermination(), so the program may never terminate correctly.
+2 Final message print repeatedly inside the while loop. Don't need to call await command in the loop. Sequence would be
+   await()  --&gt; Ensures that wait till thread is called.
+   print final message.
+4. Incorrect usage of latch. Latch is used more like an end condition, not a start coordination mechanism.
+Question 3 - Sets &amp; Dictionary 
+1. Following section of code is not correctly implemented. It will return all the words in the phrase.
+        for(String word : set){
+            if (word.startsWith(sb.toString()));{
+                set2.add(word);
+            }
+        }
+2. Result is not as per expectation.</t>
+  </si>
+  <si>
+    <t>Question 1 -  Java Socket Client Implementation 
+Program is incomplete. There is no steps to send the information to server and receive response. Some of the issue with code
+1. Socket is created but never connected to localhost:12345. Attempts to get input/output streams from an unconnected socket.
+2. User prompt to capture user input is missing.
+3. No loop to send input. No EXIT handling and No server response reading/output.
+Question 2 - Multithreading with coordination
+I have found several issues with the code as follows
+1. gate.await() is inside the task creation loop, so the program will block on the first iteration.
+2. countDown() happens after await(), resulting in incomplete latch logic
+3. Worker task does not print start/completion messages.
+4. Sleep time is fixed at 100 ms, not random 1–20 seconds. Tasks are not coordinated to start together.
+Question 3 - Sets &amp; Dictionary 
+1. Incomplete program.
+2. GetWords is missing Implementation
+3. Invalid syntax: new String[];, while(True), and code outside a method.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -253,8 +395,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,6 +419,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -302,7 +463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -327,13 +488,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -656,11 +820,12 @@
   <cols>
     <col min="1" max="1" width="40.28515625" style="6" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="43.28515625" style="6" customWidth="1"/>
-    <col min="4" max="5" width="49" style="6" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" style="6" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" style="6" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="63.28515625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="92" style="6" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
@@ -690,63 +855,107 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="13" t="s">
         <v>14</v>
+      </c>
+      <c r="C2" s="6">
+        <v>40</v>
+      </c>
+      <c r="D2" s="6">
+        <v>38</v>
+      </c>
+      <c r="E2" s="6">
+        <v>19</v>
       </c>
       <c r="F2" s="6">
         <f>SUM(C2:E2)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="270" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="13" t="s">
         <v>15</v>
+      </c>
+      <c r="C3" s="6">
+        <v>32</v>
+      </c>
+      <c r="D3" s="6">
+        <v>40</v>
+      </c>
+      <c r="E3" s="6">
+        <v>10</v>
       </c>
       <c r="F3" s="6">
         <f t="shared" ref="F3:F13" si="0">SUM(C3:E3)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="405" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="13" t="s">
         <v>16</v>
+      </c>
+      <c r="C4" s="6">
+        <v>37</v>
+      </c>
+      <c r="D4" s="6">
+        <v>30</v>
+      </c>
+      <c r="E4" s="6">
+        <v>12</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="13" t="s">
         <v>17</v>
+      </c>
+      <c r="C5" s="6">
+        <v>39</v>
+      </c>
+      <c r="D5" s="6">
+        <v>38</v>
+      </c>
+      <c r="E5" s="6">
+        <v>19</v>
       </c>
       <c r="F5" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="6">
@@ -755,96 +964,176 @@
       </c>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:8" ht="255" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="13" t="s">
         <v>19</v>
+      </c>
+      <c r="C7" s="6">
+        <v>32</v>
+      </c>
+      <c r="D7" s="6">
+        <v>26</v>
+      </c>
+      <c r="E7" s="6">
+        <v>20</v>
       </c>
       <c r="F7" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="345" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="13" t="s">
         <v>20</v>
+      </c>
+      <c r="C8" s="6">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6">
+        <v>26</v>
+      </c>
+      <c r="E8" s="6">
+        <v>9</v>
       </c>
       <c r="F8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6">
+        <v>70</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="13" t="s">
         <v>21</v>
+      </c>
+      <c r="C9" s="6">
+        <v>38</v>
+      </c>
+      <c r="D9" s="6">
+        <v>40</v>
+      </c>
+      <c r="E9" s="6">
+        <v>19</v>
       </c>
       <c r="F9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="13" t="s">
         <v>22</v>
+      </c>
+      <c r="C10" s="6">
+        <v>40</v>
+      </c>
+      <c r="D10" s="6">
+        <v>40</v>
+      </c>
+      <c r="E10" s="6">
+        <v>17</v>
       </c>
       <c r="F10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="13" t="s">
         <v>23</v>
+      </c>
+      <c r="C11" s="6">
+        <v>40</v>
+      </c>
+      <c r="D11" s="6">
+        <v>36</v>
+      </c>
+      <c r="E11" s="6">
+        <v>19</v>
       </c>
       <c r="F11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="195" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="13" t="s">
         <v>24</v>
+      </c>
+      <c r="C12" s="6">
+        <v>39</v>
+      </c>
+      <c r="D12" s="6">
+        <v>40</v>
+      </c>
+      <c r="E12" s="6">
+        <v>20</v>
       </c>
       <c r="F12" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="225" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="C13" s="6">
+        <v>40</v>
+      </c>
+      <c r="D13" s="6">
+        <v>38</v>
+      </c>
+      <c r="E13" s="6">
+        <v>18</v>
+      </c>
       <c r="F13" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B19">
